--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487753_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487753_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3571</v>
+        <v>3.6813</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8344</v>
+        <v>4.995</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4773</v>
+        <v>-1.3138</v>
       </c>
       <c r="G2" t="n">
         <v>0.9295</v>
@@ -610,13 +610,13 @@
         <v>0.7761</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5336</v>
+        <v>-0.2094</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4116</v>
+        <v>-0.251</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.122</v>
+        <v>0.0415</v>
       </c>
       <c r="V2" t="n">
         <v>3.1552</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3725</v>
+        <v>1.7423</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4426</v>
+        <v>2.7034</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0702</v>
+        <v>-0.9611</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0604</v>
@@ -688,13 +688,13 @@
         <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2373</v>
+        <v>-0.8675</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5451</v>
+        <v>-0.2843</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6922</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>1.506</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. MONZÓN RODRÍGUEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3822</v>
+        <v>-0.2272</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7279</v>
+        <v>0.8633</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3457</v>
+        <v>-1.0905</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4004</v>
+        <v>-0.5777</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6673</v>
+        <v>-2.2137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2669</v>
+        <v>1.6361</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6673</v>
+        <v>1.3995</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6673</v>
+        <v>-0.5314</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.9309</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2669</v>
+        <v>-1.9771</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.6824</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2669</v>
+        <v>-0.2948</v>
       </c>
       <c r="P4" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>0.194</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1759</v>
+        <v>-1.5615</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0606</v>
+        <v>-0.7899</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1153</v>
+        <v>-0.7716</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9418</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>Y. MONZÓN RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.582</v>
+        <v>-0.355</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5629999999999999</v>
+        <v>-0.7279</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.145</v>
+        <v>0.3729</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5777</v>
+        <v>-0.4004</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.2137</v>
+        <v>-0.6673</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6361</v>
+        <v>0.2669</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3995</v>
+        <v>-0.6673</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5314</v>
+        <v>-0.6673</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9309</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9771</v>
+        <v>0.2669</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6824</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2948</v>
+        <v>0.2669</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>0.194</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9163</v>
+        <v>-0.1486</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0902</v>
+        <v>-0.0606</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9418</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1321</v>
+        <v>-1.2689</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0698</v>
+        <v>-0.3701</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0624</v>
+        <v>-0.8988</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5494</v>
@@ -922,13 +922,13 @@
         <v>2.7164</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2245</v>
+        <v>-1.3613</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1683</v>
+        <v>-0.4686</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0563</v>
+        <v>-0.8927</v>
       </c>
       <c r="V6" t="n">
         <v>1.8358</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>A. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2246</v>
+        <v>-2.4412</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.513</v>
+        <v>0.712</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7116</v>
+        <v>-3.1533</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0652</v>
+        <v>-0.1297</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.132</v>
+        <v>0.1022</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9332</v>
+        <v>-0.2319</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2283</v>
+        <v>0.6997</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0659</v>
+        <v>0.6591</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1624</v>
+        <v>0.0406</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2935</v>
+        <v>-0.8294</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1979</v>
+        <v>-0.5569</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0956</v>
+        <v>-0.2725</v>
       </c>
       <c r="P7" t="n">
         <v>0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1344</v>
+        <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0236</v>
+        <v>0.2243</v>
       </c>
       <c r="T7" t="n">
-        <v>0.305</v>
+        <v>0.0123</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3286</v>
+        <v>0.212</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3299</v>
+        <v>-2.7298</v>
       </c>
       <c r="W7" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VIDAL RODRIGUEZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3867</v>
+        <v>-2.6945</v>
       </c>
       <c r="E8" t="n">
-        <v>0.712</v>
+        <v>-1.8017</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0987</v>
+        <v>-0.8927</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1297</v>
+        <v>-0.7056</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1022</v>
+        <v>-0.2068</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2319</v>
+        <v>-0.4988</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6997</v>
+        <v>0.3413</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6591</v>
+        <v>0.968</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0406</v>
+        <v>-0.6267</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8294</v>
+        <v>-1.0469</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5569</v>
+        <v>-1.1748</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2725</v>
+        <v>0.1279</v>
       </c>
       <c r="P8" t="n">
-        <v>0.194</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
         <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2788</v>
+        <v>-0.2425</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0123</v>
+        <v>-0.2027</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2665</v>
+        <v>-0.0398</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.7298</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9308</v>
+        <v>-2.9253</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9018</v>
+        <v>-1.2137</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.029</v>
+        <v>-1.7116</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7056</v>
+        <v>-2.0652</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2068</v>
+        <v>-1.132</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4988</v>
+        <v>-0.9332</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3413</v>
+        <v>0.2283</v>
       </c>
       <c r="K9" t="n">
-        <v>0.968</v>
+        <v>0.0659</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6267</v>
+        <v>0.1624</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0469</v>
+        <v>-2.2935</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1748</v>
+        <v>-1.1979</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1279</v>
+        <v>-1.0956</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7463</v>
+        <v>0.194</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>0.194</v>
+        <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4789</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3028</v>
+        <v>-0.3957</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1761</v>
+        <v>-0.3286</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8058</v>
+        <v>-3.2725</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1298</v>
+        <v>0.3905</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.9356</v>
+        <v>-3.663</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2053</v>
@@ -1234,13 +1234,13 @@
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8244</v>
+        <v>-0.291</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4722</v>
+        <v>-0.2114</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3522</v>
+        <v>-0.0796</v>
       </c>
       <c r="V10" t="n">
         <v>0.6119</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9159</v>
+        <v>-4.1273</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0767</v>
+        <v>-2.7158</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-1.4116</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4665</v>
@@ -1312,13 +1312,13 @@
         <v>1.9403</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6866</v>
+        <v>-0.8981</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0902</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4036</v>
+        <v>-0.1688</v>
       </c>
       <c r="V11" t="n">
         <v>2.1179</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3691</v>
+        <v>-5.8691</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6573</v>
+        <v>-3.8575</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7118</v>
+        <v>-2.0116</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2051</v>
@@ -1390,13 +1390,13 @@
         <v>2.1344</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.164</v>
+        <v>-0.664</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2412</v>
+        <v>-0.4414</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0772</v>
+        <v>-0.2226</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2239</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.032</v>
+        <v>-5.9714</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4616</v>
+        <v>-1.401</v>
       </c>
       <c r="F13" t="n">
         <v>-4.5704</v>
@@ -1468,10 +1468,10 @@
         <v>2.5224</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8367</v>
+        <v>-0.7761</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4105</v>
+        <v>-0.35</v>
       </c>
       <c r="U13" t="n">
         <v>-0.4262</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-24.0316</v>
+        <v>-23.7288</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.726300000000001</v>
+        <v>-2.423500000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-21.3055</v>
@@ -1546,13 +1546,13 @@
         <v>17.4628</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.823</v>
+        <v>-7.520000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.4754</v>
+        <v>-4.172599999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.3477</v>
+        <v>-3.3476</v>
       </c>
       <c r="V14" t="n">
         <v>2.2134</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.9718</v>
+        <v>6.2143</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1377</v>
+        <v>4.3369</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8341</v>
+        <v>1.8774</v>
       </c>
       <c r="G15" t="n">
         <v>2.7743</v>
@@ -1624,13 +1624,13 @@
         <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5274</v>
+        <v>1.7699</v>
       </c>
       <c r="T15" t="n">
-        <v>1.227</v>
+        <v>0.4262</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3004</v>
+        <v>1.3437</v>
       </c>
       <c r="V15" t="n">
         <v>0.894</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3145</v>
+        <v>4.9151</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0592</v>
+        <v>4.6598</v>
       </c>
       <c r="F16" t="n">
         <v>0.2553</v>
@@ -1702,10 +1702,10 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1581</v>
+        <v>0.4425</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7268</v>
+        <v>-0.1262</v>
       </c>
       <c r="U16" t="n">
         <v>0.5687</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8703</v>
+        <v>3.2965</v>
       </c>
       <c r="E17" t="n">
-        <v>5.0298</v>
+        <v>4.1289</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1594</v>
+        <v>-0.8324</v>
       </c>
       <c r="G17" t="n">
         <v>0.0997</v>
@@ -1780,13 +1780,13 @@
         <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9542</v>
+        <v>1.3804</v>
       </c>
       <c r="T17" t="n">
-        <v>2.076</v>
+        <v>1.1751</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1218</v>
+        <v>0.2053</v>
       </c>
       <c r="V17" t="n">
         <v>0.8462</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8501</v>
+        <v>3.2661</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1398</v>
+        <v>0.3607</v>
       </c>
       <c r="F18" t="n">
-        <v>2.99</v>
+        <v>2.9054</v>
       </c>
       <c r="G18" t="n">
         <v>0.7164</v>
@@ -1858,13 +1858,13 @@
         <v>2.3284</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0007</v>
+        <v>0.4153</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.424</v>
+        <v>0.0765</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4233</v>
+        <v>0.3387</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0748</v>
+        <v>2.7355</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7796</v>
+        <v>1.9798</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2952</v>
+        <v>0.7557</v>
       </c>
       <c r="G19" t="n">
         <v>2.2675</v>
@@ -1936,13 +1936,13 @@
         <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>0.061</v>
+        <v>0.7217</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0134</v>
+        <v>0.2136</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0476</v>
+        <v>0.5081</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2239</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.072</v>
+        <v>2.5329</v>
       </c>
       <c r="E20" t="n">
-        <v>2.486</v>
+        <v>1.8254</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.414</v>
+        <v>0.7075</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1901</v>
+        <v>-0.1281</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8741</v>
+        <v>-1.4723</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6840000000000001</v>
+        <v>1.3442</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0916</v>
+        <v>1.6985</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0916</v>
+        <v>-0.2018</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.9003</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9015</v>
+        <v>-1.8266</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2175</v>
+        <v>-1.2704</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.5561</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3881</v>
+        <v>-0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.194</v>
+        <v>-3.1045</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5821</v>
+        <v>2.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>0.552</v>
+        <v>0.7371</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3645</v>
+        <v>0.5016</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1875</v>
+        <v>0.2355</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9418</v>
+        <v>2.1179</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2239</v>
+        <v>2.7298</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2821</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0081</v>
+        <v>1.8986</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6353</v>
+        <v>1.335</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3728</v>
+        <v>0.5636</v>
       </c>
       <c r="G21" t="n">
         <v>0.8893</v>
@@ -2092,13 +2092,13 @@
         <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4188</v>
+        <v>0.3093</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2557</v>
+        <v>-0.0446</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1631</v>
+        <v>0.3539</v>
       </c>
       <c r="V21" t="n">
         <v>0.894</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6509</v>
+        <v>1.7989</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3249</v>
+        <v>2.1857</v>
       </c>
       <c r="F22" t="n">
-        <v>0.326</v>
+        <v>-0.3867</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1281</v>
+        <v>0.1901</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4723</v>
+        <v>0.8741</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3442</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6985</v>
+        <v>1.0916</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2018</v>
+        <v>1.0916</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9003</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8266</v>
+        <v>-0.9015</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2704</v>
+        <v>-0.2175</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5561</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P22" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.194</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-3.1045</v>
-      </c>
       <c r="R22" t="n">
-        <v>2.9105</v>
+        <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1449</v>
+        <v>0.279</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0011</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.146</v>
+        <v>0.2148</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1179</v>
+        <v>0.9418</v>
       </c>
       <c r="W22" t="n">
-        <v>2.7298</v>
+        <v>1.2239</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6119</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5214</v>
+        <v>0.2817</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9428</v>
+        <v>1.5424</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4214</v>
+        <v>-1.2607</v>
       </c>
       <c r="G23" t="n">
         <v>2.1378</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0253</v>
+        <v>0.7857</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.5709</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0541</v>
+        <v>0.2148</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4477</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.551</v>
+        <v>0.1859</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1794</v>
+        <v>0.78</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7305</v>
+        <v>-0.5942</v>
       </c>
       <c r="G24" t="n">
         <v>1.1816</v>
@@ -2326,13 +2326,13 @@
         <v>1.3582</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.646</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3511</v>
+        <v>0.2495</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2602</v>
+        <v>0.3965</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8358</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.3097</v>
+        <v>-1.1768</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.801</v>
+        <v>-1.1013</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5087</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5323</v>
@@ -2404,13 +2404,13 @@
         <v>2.3284</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1763</v>
+        <v>0.3093</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2434</v>
+        <v>-0.0569</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.3662</v>
       </c>
       <c r="V25" t="n">
         <v>-2.1179</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.4415</v>
+        <v>-1.2497</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.3282</v>
+        <v>-0.7276</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1133</v>
+        <v>-0.5221</v>
       </c>
       <c r="G26" t="n">
         <v>0.8918</v>
@@ -2482,13 +2482,13 @@
         <v>1.5523</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.6943</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3028</v>
+        <v>0.2978</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8053</v>
+        <v>0.3965</v>
       </c>
       <c r="V26" t="n">
         <v>-2.4477</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>24.0317</v>
+        <v>24.699</v>
       </c>
       <c r="E27" t="n">
-        <v>21.3057</v>
+        <v>21.30570000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>2.726099999999999</v>
+        <v>3.393400000000001</v>
       </c>
       <c r="G27" t="n">
         <v>12.6011</v>
@@ -2560,13 +2560,13 @@
         <v>23.2839</v>
       </c>
       <c r="S27" t="n">
-        <v>7.823</v>
+        <v>8.490500000000001</v>
       </c>
       <c r="T27" t="n">
         <v>3.3477</v>
       </c>
       <c r="U27" t="n">
-        <v>4.4753</v>
+        <v>5.1427</v>
       </c>
       <c r="V27" t="n">
         <v>-2.2134</v>
